--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ASDevice</t>
+    <t>AsDeviceProfile</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>AS Device</t>
+    <t>As Device Profile</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:35:39+00:00</t>
+    <t>2023-04-05T10:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -625,7 +625,7 @@
     <t>periodImplantation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/Device-PeriodImplantation}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-Period-implantation}
 </t>
   </si>
   <si>
@@ -1862,7 +1862,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="112.93359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="119.6484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T10:55:45+00:00</t>
+    <t>2023-04-05T15:18:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:18:36+00:00</t>
+    <t>2023-04-05T15:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:41:27+00:00</t>
+    <t>2023-04-05T15:52:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:52:08+00:00</t>
+    <t>2023-04-05T15:53:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:53:16+00:00</t>
+    <t>2023-04-05T15:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="440">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:55:13+00:00</t>
+    <t>2023-04-05T16:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1111,163 +1111,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J135-EquipementMaterielLourd-RASS/FHIR/JDV-J135-EquipementMaterielLourd-RASS</t>
-  </si>
-  <si>
-    <t>Device.type.id</t>
-  </si>
-  <si>
-    <t>Device.type.extension</t>
-  </si>
-  <si>
-    <t>Device.type.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Device.type.coding.id</t>
-  </si>
-  <si>
-    <t>Device.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Device.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R272-EquipementMaterielLourd/FHIR/TRE-R272-EquipementMaterielLourd</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Device.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Device.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Device.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Device.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Device.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1849,7 +1692,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM89"/>
+  <dimension ref="A1:AM78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.8515625" customWidth="true" bestFit="true"/>
@@ -7460,7 +7303,7 @@
         <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -7472,13 +7315,13 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>98</v>
+        <v>348</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>99</v>
+        <v>349</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7529,19 +7372,19 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>100</v>
+        <v>347</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>101</v>
@@ -7555,21 +7398,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -7581,17 +7424,15 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>74</v>
@@ -7628,34 +7469,34 @@
         <v>74</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>74</v>
@@ -7666,14 +7507,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7689,23 +7530,21 @@
         <v>74</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>350</v>
+        <v>105</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>351</v>
+        <v>106</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>74</v>
       </c>
@@ -7741,19 +7580,19 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>354</v>
+        <v>111</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7765,10 +7604,10 @@
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>355</v>
+        <v>95</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>74</v>
@@ -7779,42 +7618,46 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>74</v>
       </c>
@@ -7862,22 +7705,22 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>74</v>
@@ -7888,21 +7731,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>103</v>
+        <v>326</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -7914,16 +7757,16 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>104</v>
+        <v>282</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>107</v>
+        <v>285</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7961,34 +7804,34 @@
         <v>74</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>111</v>
+        <v>353</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>74</v>
@@ -7999,10 +7842,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8022,29 +7865,27 @@
         <v>74</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>363</v>
+        <v>74</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>74</v>
@@ -8086,7 +7927,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -8101,10 +7942,10 @@
         <v>94</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>365</v>
+        <v>101</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>74</v>
@@ -8112,10 +7953,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8126,7 +7967,7 @@
         <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>74</v>
@@ -8135,20 +7976,18 @@
         <v>74</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>74</v>
@@ -8197,13 +8036,13 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>93</v>
@@ -8212,7 +8051,7 @@
         <v>94</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>371</v>
+        <v>101</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>74</v>
@@ -8223,10 +8062,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8246,23 +8085,19 @@
         <v>74</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>373</v>
+        <v>98</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>74</v>
       </c>
@@ -8310,7 +8145,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>376</v>
+        <v>100</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -8319,13 +8154,13 @@
         <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>377</v>
+        <v>101</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>74</v>
@@ -8336,21 +8171,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>74</v>
@@ -8359,23 +8194,21 @@
         <v>74</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>379</v>
+        <v>105</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>380</v>
+        <v>106</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>74</v>
       </c>
@@ -8411,34 +8244,34 @@
         <v>74</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>382</v>
+        <v>111</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>383</v>
+        <v>95</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>74</v>
@@ -8449,45 +8282,45 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>385</v>
+        <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>386</v>
+        <v>229</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>387</v>
+        <v>230</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>388</v>
+        <v>107</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>389</v>
+        <v>202</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>74</v>
@@ -8536,22 +8369,22 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>390</v>
+        <v>231</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>391</v>
+        <v>95</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>74</v>
@@ -8562,14 +8395,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>74</v>
+        <v>326</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8585,23 +8418,21 @@
         <v>74</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>97</v>
+        <v>282</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>74</v>
       </c>
@@ -8649,7 +8480,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>397</v>
+        <v>365</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8664,7 +8495,7 @@
         <v>94</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>398</v>
+        <v>288</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>74</v>
@@ -8675,10 +8506,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8689,7 +8520,7 @@
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -8701,13 +8532,13 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8758,13 +8589,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>93</v>
@@ -8773,10 +8604,10 @@
         <v>94</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>101</v>
+        <v>371</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>74</v>
@@ -8784,10 +8615,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8795,7 +8626,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>81</v>
@@ -8813,12 +8644,14 @@
         <v>97</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>98</v>
+        <v>373</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>74</v>
@@ -8867,19 +8700,19 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>100</v>
+        <v>372</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>101</v>
@@ -8893,21 +8726,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>74</v>
@@ -8919,17 +8752,15 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>104</v>
+        <v>220</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>105</v>
+        <v>376</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>74</v>
@@ -8966,19 +8797,19 @@
         <v>74</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>111</v>
+        <v>375</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -8990,10 +8821,10 @@
         <v>93</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>74</v>
@@ -9004,46 +8835,42 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>74</v>
       </c>
@@ -9091,22 +8918,22 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>231</v>
+        <v>100</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>74</v>
@@ -9117,21 +8944,21 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>326</v>
+        <v>103</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -9143,16 +8970,16 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>282</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>406</v>
+        <v>105</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>407</v>
+        <v>106</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>285</v>
+        <v>107</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9190,34 +9017,34 @@
         <v>74</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>405</v>
+        <v>111</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>288</v>
+        <v>95</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>74</v>
@@ -9228,44 +9055,46 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>409</v>
+        <v>229</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>410</v>
+        <v>230</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>74</v>
       </c>
@@ -9313,25 +9142,25 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>408</v>
+        <v>231</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>74</v>
@@ -9339,10 +9168,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9350,10 +9179,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>74</v>
@@ -9365,15 +9194,17 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>74</v>
@@ -9422,13 +9253,13 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>93</v>
@@ -9437,7 +9268,7 @@
         <v>94</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>74</v>
@@ -9448,10 +9279,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9462,7 +9293,7 @@
         <v>75</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -9474,15 +9305,17 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>97</v>
+        <v>385</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>98</v>
+        <v>386</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>74</v>
@@ -9531,22 +9364,22 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>100</v>
+        <v>384</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>74</v>
+        <v>389</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>101</v>
+        <v>390</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>74</v>
@@ -9557,14 +9390,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9583,16 +9416,16 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>104</v>
+        <v>282</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>105</v>
+        <v>392</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>106</v>
+        <v>393</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>107</v>
+        <v>285</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9630,19 +9463,19 @@
         <v>74</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>111</v>
+        <v>391</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9654,10 +9487,10 @@
         <v>93</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>74</v>
@@ -9668,45 +9501,45 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>104</v>
+        <v>395</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>229</v>
+        <v>396</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>230</v>
+        <v>397</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>107</v>
+        <v>216</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>202</v>
+        <v>398</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>74</v>
@@ -9755,25 +9588,25 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>231</v>
+        <v>394</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>112</v>
+        <v>217</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>95</v>
+        <v>399</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>74</v>
+        <v>400</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>74</v>
@@ -9781,14 +9614,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>326</v>
+        <v>74</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9807,16 +9640,16 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>282</v>
+        <v>402</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>285</v>
+        <v>405</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9866,7 +9699,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -9878,13 +9711,13 @@
         <v>93</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>288</v>
+        <v>406</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>74</v>
+        <v>407</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>74</v>
@@ -9892,10 +9725,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9906,7 +9739,7 @@
         <v>75</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>74</v>
@@ -9918,15 +9751,17 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>205</v>
+        <v>409</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>74</v>
@@ -9975,25 +9810,25 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>94</v>
+        <v>413</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>238</v>
+        <v>407</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>74</v>
@@ -10001,10 +9836,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10012,10 +9847,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>74</v>
@@ -10027,18 +9862,20 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>97</v>
+        <v>416</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>74</v>
       </c>
@@ -10086,10 +9923,10 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>81</v>
@@ -10098,13 +9935,13 @@
         <v>93</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>101</v>
+        <v>420</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>74</v>
+        <v>421</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>74</v>
@@ -10112,10 +9949,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10138,15 +9975,17 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>74</v>
@@ -10195,13 +10034,13 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>93</v>
@@ -10210,10 +10049,10 @@
         <v>94</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>101</v>
+        <v>426</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>74</v>
+        <v>421</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>74</v>
@@ -10221,10 +10060,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10235,7 +10074,7 @@
         <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>74</v>
@@ -10247,15 +10086,17 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>97</v>
+        <v>428</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>98</v>
+        <v>429</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>74</v>
@@ -10304,22 +10145,22 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>100</v>
+        <v>427</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>101</v>
+        <v>432</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>74</v>
@@ -10330,21 +10171,21 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>74</v>
@@ -10353,19 +10194,19 @@
         <v>74</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>104</v>
+        <v>282</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>105</v>
+        <v>434</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>106</v>
+        <v>435</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>107</v>
+        <v>285</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10403,19 +10244,19 @@
         <v>74</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>111</v>
+        <v>433</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -10427,10 +10268,10 @@
         <v>93</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>74</v>
@@ -10441,46 +10282,44 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>104</v>
+        <v>437</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>229</v>
+        <v>438</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>230</v>
+        <v>439</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>74</v>
       </c>
@@ -10528,1252 +10367,27 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>231</v>
+        <v>436</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>112</v>
+        <v>217</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>95</v>
+        <v>218</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM89" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:00:25+00:00</t>
+    <t>2023-04-05T16:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:20:25+00:00</t>
+    <t>2023-04-05T16:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:21:30+00:00</t>
+    <t>2023-04-05T16:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:24:37+00:00</t>
+    <t>2023-04-05T17:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T17:39:15+00:00</t>
+    <t>2023-04-07T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-07T12:42:40+00:00</t>
+    <t>2023-04-12T10:00:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:00:48+00:00</t>
+    <t>2023-04-12T10:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:05:52+00:00</t>
+    <t>2023-04-12T10:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:08:35+00:00</t>
+    <t>2023-04-12T14:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T14:03:54+00:00</t>
+    <t>2023-04-13T07:49:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T07:49:09+00:00</t>
+    <t>2023-04-13T08:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:12:13+00:00</t>
+    <t>2023-04-13T08:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:22:34+00:00</t>
+    <t>2023-04-13T08:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:33:21+00:00</t>
+    <t>2023-04-13T08:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$70</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="399">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:34:34+00:00</t>
+    <t>2023-04-13T08:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -308,7 +311,268 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Device.meta.id</t>
+    <t>Device.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Device.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Device.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Device.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>Device.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Device.extension:numberAuthorizationARHGOS</t>
+  </si>
+  <si>
+    <t>numberAuthorizationARHGOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/Device-numberAuthorizationARHGOS}
+</t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t>Device.extension:authorizationDateDevice</t>
+  </si>
+  <si>
+    <t>authorizationDateDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/Device-authorizationDateDevice}
+</t>
+  </si>
+  <si>
+    <t>Device.extension:periodImplantation</t>
+  </si>
+  <si>
+    <t>periodImplantation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-Period-implantation}
+</t>
+  </si>
+  <si>
+    <t>Dates de mise en oeuvre de l'EML</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte des dates de mise en oeuvre d’un équipement matériel lourd.</t>
+  </si>
+  <si>
+    <t>Device.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Device.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Numéro autorisation ARGHOS</t>
+  </si>
+  <si>
+    <t>Unique instance identifiers assigned to a device by manufacturers other organizations or owners.</t>
+  </si>
+  <si>
+    <t>The barcode string from a barcode present on a device label or package may identify the instance, include names given to the device in local usage, or may identify the type of device. If the identifier identifies the type of device, Device.type element should be used.</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>The serial number which is a component of the production identifier (PI), a conditional, variable portion of a UDI.   The identifier.type code should be set to “SNO”(Serial Number) and the system left empty.</t>
+  </si>
+  <si>
+    <t>Device.definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DeviceDefinition)
+</t>
+  </si>
+  <si>
+    <t>The reference to the definition for the device</t>
+  </si>
+  <si>
+    <t>The reference to the definition for the device.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Unique Device Identifier (UDI) Barcode string</t>
+  </si>
+  <si>
+    <t>Unique device identifier (UDI) assigned to device label or package.  Note that the Device may include multiple udiCarriers as it either may include just the udiCarrier for the jurisdiction it is sold, or for multiple jurisdictions it could have been sold.</t>
+  </si>
+  <si>
+    <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
+  </si>
+  <si>
+    <t>.id and .code</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -324,404 +588,13 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Device.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
+    <t>Device.udiCarrier.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Device.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Device.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Device.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Device.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Device.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>Device.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Device.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Device.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Device.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Device.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>Device.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Device.extension:numberAuthorizationARHGOS</t>
-  </si>
-  <si>
-    <t>numberAuthorizationARHGOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/Device-numberAuthorizationARHGOS}
-</t>
-  </si>
-  <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>Device.extension:authorizationDateDevice</t>
-  </si>
-  <si>
-    <t>authorizationDateDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/Device-authorizationDateDevice}
-</t>
-  </si>
-  <si>
-    <t>Device.extension:periodImplantation</t>
-  </si>
-  <si>
-    <t>periodImplantation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-Period-implantation}
-</t>
-  </si>
-  <si>
-    <t>Dates de mise en oeuvre de l'EML</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte des dates de mise en oeuvre d’un équipement matériel lourd.</t>
-  </si>
-  <si>
-    <t>Device.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Device.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Numéro autorisation ARGHOS</t>
-  </si>
-  <si>
-    <t>Unique instance identifiers assigned to a device by manufacturers other organizations or owners.</t>
-  </si>
-  <si>
-    <t>The barcode string from a barcode present on a device label or package may identify the instance, include names given to the device in local usage, or may identify the type of device. If the identifier identifies the type of device, Device.type element should be used.</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>The serial number which is a component of the production identifier (PI), a conditional, variable portion of a UDI.   The identifier.type code should be set to “SNO”(Serial Number) and the system left empty.</t>
-  </si>
-  <si>
-    <t>Device.definition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DeviceDefinition)
-</t>
-  </si>
-  <si>
-    <t>The reference to the definition for the device</t>
-  </si>
-  <si>
-    <t>The reference to the definition for the device.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
-    <t>Device.udiCarrier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Unique Device Identifier (UDI) Barcode string</t>
-  </si>
-  <si>
-    <t>Unique device identifier (UDI) assigned to device label or package.  Note that the Device may include multiple udiCarriers as it either may include just the udiCarrier for the jurisdiction it is sold, or for multiple jurisdictions it could have been sold.</t>
-  </si>
-  <si>
-    <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
-  </si>
-  <si>
-    <t>.id and .code</t>
-  </si>
-  <si>
-    <t>Device.udiCarrier.id</t>
-  </si>
-  <si>
-    <t>Device.udiCarrier.extension</t>
   </si>
   <si>
     <t>Device.udiCarrier.modifierExtension</t>
@@ -924,6 +797,9 @@
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>The availability status reason of the device.</t>
@@ -1527,6 +1403,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1692,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM78"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.8515625" customWidth="true" bestFit="true"/>
@@ -1719,7 +1610,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="68.64453125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="112.0078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1854,7 +1745,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
@@ -1963,7 +1854,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>80</v>
       </c>
@@ -2074,7 +1965,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>88</v>
       </c>
@@ -2183,7 +2074,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>96</v>
       </c>
@@ -2205,10 +2096,10 @@
         <v>74</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>97</v>
@@ -2219,7 +2110,9 @@
       <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>74</v>
@@ -2268,7 +2161,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -2277,13 +2170,13 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>74</v>
@@ -2292,23 +2185,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -2355,28 +2248,28 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>111</v>
@@ -2385,34 +2278,34 @@
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM6" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" hidden="true">
+      <c r="A7" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="AK6" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM6" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2428,19 +2321,19 @@
         <v>74</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2490,7 +2383,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -2505,7 +2398,7 @@
         <v>94</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>74</v>
@@ -2514,23 +2407,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -2539,19 +2432,19 @@
         <v>74</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2601,22 +2494,22 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>74</v>
@@ -2625,23 +2518,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>74</v>
@@ -2650,19 +2543,19 @@
         <v>74</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2700,34 +2593,34 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>74</v>
@@ -2736,14 +2629,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
@@ -2752,29 +2647,27 @@
         <v>75</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -2823,7 +2716,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -2835,10 +2728,10 @@
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>74</v>
@@ -2847,14 +2740,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2863,29 +2758,27 @@
         <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>74</v>
@@ -2910,13 +2803,13 @@
         <v>74</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>74</v>
@@ -2934,7 +2827,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2946,10 +2839,10 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>74</v>
@@ -2958,14 +2851,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>146</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>74</v>
       </c>
@@ -2974,29 +2869,27 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>74</v>
@@ -3021,13 +2914,13 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -3045,7 +2938,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -3057,10 +2950,10 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>74</v>
@@ -3069,23 +2962,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -3094,21 +2987,23 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>74</v>
       </c>
@@ -3144,34 +3039,34 @@
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>74</v>
@@ -3180,12 +3075,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3196,7 +3091,7 @@
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>
@@ -3208,16 +3103,16 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3243,13 +3138,13 @@
         <v>74</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -3267,13 +3162,13 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>93</v>
@@ -3282,35 +3177,35 @@
         <v>94</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>74</v>
+        <v>163</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>74</v>
@@ -3319,16 +3214,16 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3378,7 +3273,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3390,10 +3285,10 @@
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>74</v>
@@ -3402,44 +3297,44 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3489,7 +3384,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3498,38 +3393,38 @@
         <v>76</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -3541,17 +3436,15 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>74</v>
@@ -3588,34 +3481,34 @@
         <v>74</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>74</v>
@@ -3624,25 +3517,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>74</v>
@@ -3654,15 +3545,17 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>129</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>74</v>
@@ -3699,19 +3592,19 @@
         <v>74</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3723,7 +3616,7 @@
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>95</v>
@@ -3735,46 +3628,48 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>129</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>74</v>
       </c>
@@ -3822,7 +3717,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3834,7 +3729,7 @@
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>95</v>
@@ -3846,18 +3741,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3873,18 +3766,20 @@
         <v>74</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>74</v>
@@ -3933,59 +3828,59 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>74</v>
+        <v>195</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>74</v>
+        <v>197</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>200</v>
@@ -3994,11 +3889,9 @@
         <v>201</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O21" t="s" s="2">
         <v>202</v>
       </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>74</v>
       </c>
@@ -4034,48 +3927,48 @@
         <v>74</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>74</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4086,7 +3979,7 @@
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -4098,7 +3991,7 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>205</v>
+        <v>97</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>206</v>
@@ -4107,9 +4000,11 @@
         <v>207</v>
       </c>
       <c r="N22" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>74</v>
       </c>
@@ -4157,13 +4052,13 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>93</v>
@@ -4175,29 +4070,29 @@
         <v>209</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
+      <c r="A23" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>74</v>
+        <v>211</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -4206,19 +4101,19 @@
         <v>74</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4268,7 +4163,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4280,35 +4175,35 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AK23" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>219</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -4320,16 +4215,16 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4379,13 +4274,13 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>93</v>
@@ -4394,21 +4289,21 @@
         <v>94</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>210</v>
+        <v>74</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>74</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4431,16 +4326,20 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>98</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>74</v>
       </c>
@@ -4464,13 +4363,13 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>74</v>
+        <v>229</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -4488,7 +4387,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>100</v>
+        <v>223</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4497,13 +4396,13 @@
         <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>74</v>
@@ -4512,44 +4411,44 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4575,64 +4474,64 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>74</v>
+        <v>236</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>95</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4642,29 +4541,27 @@
         <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>74</v>
       </c>
@@ -4688,13 +4585,13 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>74</v>
+        <v>245</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -4712,7 +4609,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4724,28 +4621,28 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4755,25 +4652,25 @@
         <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4823,7 +4720,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4838,25 +4735,25 @@
         <v>94</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>239</v>
+        <v>254</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>241</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4875,16 +4772,16 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>244</v>
+        <v>194</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4934,7 +4831,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4949,21 +4846,21 @@
         <v>94</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>246</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4977,7 +4874,7 @@
         <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4986,20 +4883,16 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>125</v>
+        <v>260</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>74</v>
       </c>
@@ -5047,7 +4940,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -5062,25 +4955,25 @@
         <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>74</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>253</v>
+        <v>74</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5090,26 +4983,24 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>74</v>
@@ -5158,7 +5049,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5173,25 +5064,25 @@
         <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>260</v>
+        <v>74</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5201,25 +5092,25 @@
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5269,7 +5160,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5284,21 +5175,21 @@
         <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5321,20 +5212,18 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>74</v>
       </c>
@@ -5358,13 +5247,13 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>270</v>
+        <v>74</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>271</v>
+        <v>74</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -5382,7 +5271,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5397,21 +5286,21 @@
         <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5422,29 +5311,27 @@
         <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>74</v>
@@ -5469,37 +5356,37 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>277</v>
+        <v>74</v>
       </c>
       <c r="Z34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AA34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>93</v>
@@ -5508,16 +5395,16 @@
         <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>102</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>280</v>
+        <v>74</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>281</v>
       </c>
@@ -5533,7 +5420,7 @@
         <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>74</v>
@@ -5545,17 +5432,15 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -5580,13 +5465,13 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>286</v>
+        <v>74</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>287</v>
+        <v>74</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -5604,47 +5489,47 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>288</v>
+        <v>102</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>280</v>
+        <v>74</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>290</v>
+        <v>128</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
@@ -5656,16 +5541,16 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>291</v>
+        <v>130</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>292</v>
+        <v>183</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>293</v>
+        <v>132</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5703,82 +5588,84 @@
         <v>74</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>289</v>
+        <v>184</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>294</v>
+        <v>95</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>295</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>297</v>
+        <v>187</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>298</v>
+        <v>188</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
       </c>
@@ -5826,47 +5713,47 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>296</v>
+        <v>189</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>299</v>
+        <v>95</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>74</v>
+        <v>285</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>74</v>
@@ -5878,15 +5765,17 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>301</v>
+        <v>178</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>74</v>
@@ -5935,10 +5824,10 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>81</v>
@@ -5950,21 +5839,21 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>305</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5972,10 +5861,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -5987,15 +5876,17 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>301</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -6020,13 +5911,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>74</v>
+        <v>291</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>74</v>
+        <v>292</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -6044,10 +5935,10 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>81</v>
@@ -6059,21 +5950,21 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>310</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6084,10 +5975,10 @@
         <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -6096,16 +5987,16 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6155,7 +6046,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6170,21 +6061,21 @@
         <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>295</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6198,7 +6089,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -6207,16 +6098,16 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6266,7 +6157,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6281,21 +6172,21 @@
         <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>318</v>
+        <v>277</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6306,7 +6197,7 @@
         <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>74</v>
@@ -6318,15 +6209,17 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>74</v>
@@ -6351,13 +6244,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>74</v>
+        <v>304</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>74</v>
+        <v>305</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -6375,13 +6268,13 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>93</v>
@@ -6390,7 +6283,7 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>101</v>
+        <v>247</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>74</v>
@@ -6399,12 +6292,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6415,10 +6308,10 @@
         <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -6427,13 +6320,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>98</v>
+        <v>307</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>99</v>
+        <v>308</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6484,22 +6377,22 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>100</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>74</v>
@@ -6508,23 +6401,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>74</v>
@@ -6536,17 +6429,15 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>74</v>
@@ -6583,34 +6474,34 @@
         <v>74</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>74</v>
@@ -6619,16 +6510,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>228</v>
+        <v>128</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6641,26 +6532,24 @@
         <v>74</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>229</v>
+        <v>130</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -6696,19 +6585,19 @@
         <v>74</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6720,7 +6609,7 @@
         <v>93</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>95</v>
@@ -6732,46 +6621,48 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>326</v>
+        <v>186</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>327</v>
+        <v>187</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>328</v>
+        <v>188</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -6819,22 +6710,22 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>325</v>
+        <v>189</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>74</v>
@@ -6843,16 +6734,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>74</v>
+        <v>285</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6871,16 +6762,16 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6906,13 +6797,13 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>332</v>
+        <v>74</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>333</v>
+        <v>74</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -6930,7 +6821,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6945,21 +6836,21 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>334</v>
+        <v>247</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6970,7 +6861,7 @@
         <v>75</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>74</v>
@@ -6982,16 +6873,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7041,7 +6932,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -7056,21 +6947,21 @@
         <v>94</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>338</v>
+        <v>102</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7081,10 +6972,10 @@
         <v>75</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>74</v>
@@ -7093,17 +6984,15 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>74</v>
@@ -7152,13 +7041,13 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>93</v>
@@ -7167,21 +7056,21 @@
         <v>94</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>318</v>
+        <v>102</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7204,17 +7093,15 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>343</v>
+        <v>179</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -7239,13 +7126,13 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>345</v>
+        <v>74</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>346</v>
+        <v>74</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -7263,7 +7150,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>181</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7272,13 +7159,13 @@
         <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>288</v>
+        <v>102</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>74</v>
@@ -7287,23 +7174,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -7315,15 +7202,17 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>348</v>
+        <v>130</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>74</v>
@@ -7360,19 +7249,19 @@
         <v>74</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>347</v>
+        <v>184</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7384,10 +7273,10 @@
         <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>74</v>
@@ -7396,44 +7285,48 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>98</v>
+        <v>187</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -7481,22 +7374,22 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>74</v>
@@ -7505,23 +7398,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>103</v>
+        <v>285</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -7533,16 +7426,16 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>105</v>
+        <v>325</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>106</v>
+        <v>326</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7580,34 +7473,34 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>111</v>
+        <v>324</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>74</v>
@@ -7616,48 +7509,44 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>352</v>
+        <v>327</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>352</v>
+        <v>327</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>229</v>
+        <v>328</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>74</v>
       </c>
@@ -7705,40 +7594,40 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>231</v>
+        <v>327</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>95</v>
+        <v>330</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>326</v>
+        <v>74</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7757,16 +7646,16 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>285</v>
+        <v>194</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7816,7 +7705,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7831,7 +7720,7 @@
         <v>94</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>288</v>
+        <v>102</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>74</v>
@@ -7840,12 +7729,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7856,10 +7745,10 @@
         <v>75</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>74</v>
@@ -7868,17 +7757,15 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>74</v>
@@ -7927,13 +7814,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>93</v>
@@ -7942,21 +7829,21 @@
         <v>94</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7967,7 +7854,7 @@
         <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>74</v>
@@ -7979,13 +7866,13 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>360</v>
+        <v>179</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>361</v>
+        <v>180</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8036,22 +7923,22 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>359</v>
+        <v>181</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>74</v>
@@ -8060,23 +7947,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -8088,15 +7975,17 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>74</v>
@@ -8133,34 +8022,34 @@
         <v>74</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>74</v>
@@ -8169,16 +8058,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8191,24 +8080,26 @@
         <v>74</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>74</v>
       </c>
@@ -8244,19 +8135,19 @@
         <v>74</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8268,7 +8159,7 @@
         <v>93</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>95</v>
@@ -8280,48 +8171,46 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>229</v>
+        <v>341</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>230</v>
+        <v>342</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>74</v>
       </c>
@@ -8369,22 +8258,22 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>231</v>
+        <v>340</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>74</v>
@@ -8393,23 +8282,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>326</v>
+        <v>74</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>74</v>
@@ -8421,16 +8310,16 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>282</v>
+        <v>344</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>285</v>
+        <v>347</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8480,22 +8369,22 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>94</v>
+        <v>348</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>288</v>
+        <v>349</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>74</v>
@@ -8504,12 +8393,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8520,7 +8409,7 @@
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -8532,15 +8421,17 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>74</v>
@@ -8589,13 +8480,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>93</v>
@@ -8604,21 +8495,21 @@
         <v>94</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>371</v>
+        <v>247</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8626,13 +8517,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>74</v>
@@ -8641,18 +8532,20 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>97</v>
+        <v>354</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>74</v>
       </c>
@@ -8700,10 +8593,10 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>81</v>
@@ -8712,24 +8605,24 @@
         <v>93</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>101</v>
+        <v>358</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>74</v>
+        <v>359</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8740,7 +8633,7 @@
         <v>75</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>74</v>
@@ -8752,15 +8645,17 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>220</v>
+        <v>361</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>74</v>
@@ -8809,36 +8704,36 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>101</v>
+        <v>365</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>74</v>
+        <v>366</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8849,10 +8744,10 @@
         <v>75</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
@@ -8861,15 +8756,17 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>97</v>
+        <v>368</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>98</v>
+        <v>369</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>74</v>
@@ -8918,50 +8815,50 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>100</v>
+        <v>367</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>74</v>
+        <v>372</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>101</v>
+        <v>373</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>74</v>
+        <v>366</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>74</v>
@@ -8970,18 +8867,20 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>375</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>105</v>
+        <v>376</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>106</v>
+        <v>377</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>74</v>
       </c>
@@ -9017,84 +8916,82 @@
         <v>74</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>111</v>
+        <v>374</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>95</v>
+        <v>379</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>74</v>
+        <v>380</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>229</v>
+        <v>382</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>230</v>
+        <v>383</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>74</v>
       </c>
@@ -9142,36 +9039,36 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>231</v>
+        <v>381</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>95</v>
+        <v>385</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>74</v>
+        <v>380</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9179,13 +9076,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>74</v>
@@ -9194,16 +9091,16 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>282</v>
+        <v>387</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>285</v>
+        <v>390</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9253,13 +9150,13 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>93</v>
@@ -9268,7 +9165,7 @@
         <v>94</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>288</v>
+        <v>391</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>74</v>
@@ -9277,12 +9174,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9296,25 +9193,25 @@
         <v>76</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>385</v>
+        <v>240</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>388</v>
+        <v>243</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9364,7 +9261,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9376,10 +9273,10 @@
         <v>93</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>389</v>
+        <v>94</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>390</v>
+        <v>230</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>74</v>
@@ -9388,12 +9285,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9404,10 +9301,10 @@
         <v>75</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>74</v>
@@ -9416,16 +9313,16 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>282</v>
+        <v>396</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>285</v>
+        <v>168</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9475,923 +9372,49 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>288</v>
+        <v>170</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM78" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AM70">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI69">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:54:00+00:00</t>
+    <t>2023-04-13T09:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T09:51:53+00:00</t>
+    <t>2023-04-13T10:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T10:21:56+00:00</t>
+    <t>2023-04-13T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T12:58:26+00:00</t>
+    <t>2023-04-13T15:00:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:00:08+00:00</t>
+    <t>2023-04-13T15:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:16:05+00:00</t>
+    <t>2023-04-14T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:31:23+00:00</t>
+    <t>2023-04-14T12:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:45:28+00:00</t>
+    <t>2023-04-14T13:02:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:02:26+00:00</t>
+    <t>2023-04-14T13:12:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:12:31+00:00</t>
+    <t>2023-04-17T08:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:15:24+00:00</t>
+    <t>2023-04-17T08:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:17:23+00:00</t>
+    <t>2023-04-17T08:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:37:32+00:00</t>
+    <t>2023-04-17T09:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T09:07:20+00:00</t>
+    <t>2023-04-17T10:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:39:40+00:00</t>
+    <t>2023-04-17T10:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:56:20+00:00</t>
+    <t>2023-04-17T11:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:14:19+00:00</t>
+    <t>2023-04-17T11:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:17:21+00:00</t>
+    <t>2023-04-17T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:39:02+00:00</t>
+    <t>2023-04-17T11:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:54:58+00:00</t>
+    <t>2023-04-17T12:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:02:32+00:00</t>
+    <t>2023-04-17T13:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T13:37:35+00:00</t>
+    <t>2023-04-17T14:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T14:05:09+00:00</t>
+    <t>2023-04-20T17:39:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:39:34+00:00</t>
+    <t>2023-04-20T17:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="440">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,13 +311,193 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Device.implicitRules</t>
+    <t>Device.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Device.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Device.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Device.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Device.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Device.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Device.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Device.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Device.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -328,9 +508,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>Device.language</t>
@@ -413,38 +590,10 @@
     <t>Device.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Device.extension:numberAuthorizationARHGOS</t>
@@ -575,26 +724,7 @@
     <t>Device.udiCarrier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Device.udiCarrier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Device.udiCarrier.modifierExtension</t>
@@ -797,9 +927,6 @@
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>The availability status reason of the device.</t>
@@ -1583,7 +1710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.8515625" customWidth="true" bestFit="true"/>
@@ -1610,7 +1737,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="68.64453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="112.0078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -2096,10 +2223,10 @@
         <v>74</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>97</v>
@@ -2110,9 +2237,7 @@
       <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>100</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>74</v>
@@ -2161,7 +2286,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -2170,13 +2295,13 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>74</v>
@@ -2187,21 +2312,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -2248,28 +2373,28 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AD6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>111</v>
@@ -2278,16 +2403,16 @@
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>74</v>
@@ -2298,14 +2423,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2321,19 +2446,19 @@
         <v>74</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2383,7 +2508,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -2398,7 +2523,7 @@
         <v>94</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>74</v>
@@ -2409,21 +2534,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -2432,19 +2557,19 @@
         <v>74</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2494,22 +2619,22 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>74</v>
@@ -2520,21 +2645,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>74</v>
@@ -2543,19 +2668,19 @@
         <v>74</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2593,34 +2718,34 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>74</v>
@@ -2631,14 +2756,12 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
@@ -2647,27 +2770,29 @@
         <v>75</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -2716,7 +2841,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -2728,10 +2853,10 @@
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>74</v>
@@ -2742,14 +2867,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2758,27 +2881,29 @@
         <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>74</v>
@@ -2803,13 +2928,13 @@
         <v>74</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>74</v>
@@ -2827,7 +2952,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2839,10 +2964,10 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>74</v>
@@ -2856,11 +2981,9 @@
         <v>146</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>74</v>
       </c>
@@ -2869,27 +2992,29 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K12" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>74</v>
@@ -2914,13 +3039,13 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2938,7 +3063,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2950,10 +3075,10 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>74</v>
@@ -2964,21 +3089,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2987,23 +3112,21 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>74</v>
       </c>
@@ -3039,34 +3162,34 @@
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>74</v>
@@ -3077,10 +3200,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3091,7 +3214,7 @@
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>
@@ -3103,16 +3226,16 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3138,13 +3261,13 @@
         <v>74</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -3162,13 +3285,13 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>93</v>
@@ -3177,25 +3300,25 @@
         <v>94</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>163</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3205,7 +3328,7 @@
         <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>74</v>
@@ -3214,16 +3337,16 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3273,7 +3396,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3285,10 +3408,10 @@
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>169</v>
+        <v>94</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>74</v>
@@ -3299,14 +3422,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3316,25 +3439,25 @@
         <v>76</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3384,7 +3507,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3393,16 +3516,16 @@
         <v>76</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>176</v>
+        <v>95</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>74</v>
@@ -3410,21 +3533,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -3436,15 +3559,17 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>74</v>
@@ -3481,34 +3606,34 @@
         <v>74</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>74</v>
@@ -3519,24 +3644,26 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>74</v>
@@ -3545,17 +3672,15 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>74</v>
@@ -3592,19 +3717,19 @@
         <v>74</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3616,7 +3741,7 @@
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>95</v>
@@ -3630,46 +3755,44 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>74</v>
       </c>
@@ -3717,7 +3840,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3729,7 +3852,7 @@
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>95</v>
@@ -3743,14 +3866,16 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>191</v>
+        <v>74</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3760,26 +3885,24 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>74</v>
@@ -3828,59 +3951,59 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>196</v>
+        <v>74</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>197</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>200</v>
@@ -3889,9 +4012,11 @@
         <v>201</v>
       </c>
       <c r="N21" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>74</v>
       </c>
@@ -3927,48 +4052,48 @@
         <v>74</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>203</v>
+        <v>95</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>204</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3979,7 +4104,7 @@
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3991,7 +4116,7 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>206</v>
@@ -4000,11 +4125,9 @@
         <v>207</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O22" t="s" s="2">
         <v>208</v>
       </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>74</v>
       </c>
@@ -4052,13 +4175,13 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>93</v>
@@ -4070,22 +4193,22 @@
         <v>209</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>74</v>
+        <v>210</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>74</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>211</v>
+        <v>74</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4095,25 +4218,25 @@
         <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4163,7 +4286,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4175,38 +4298,38 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>216</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>218</v>
+        <v>74</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -4215,16 +4338,16 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4274,13 +4397,13 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>93</v>
@@ -4289,21 +4412,21 @@
         <v>94</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>74</v>
+        <v>210</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>222</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4326,20 +4449,16 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>224</v>
+        <v>98</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>74</v>
       </c>
@@ -4363,13 +4482,13 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -4387,7 +4506,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>223</v>
+        <v>100</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4396,13 +4515,13 @@
         <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>230</v>
+        <v>101</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>74</v>
@@ -4413,42 +4532,42 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>106</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
+        <v>107</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4474,49 +4593,49 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>235</v>
+        <v>74</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>236</v>
+        <v>74</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>74</v>
@@ -4524,14 +4643,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4541,27 +4660,29 @@
         <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I27" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="J27" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>74</v>
       </c>
@@ -4585,13 +4706,13 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>245</v>
+        <v>74</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>246</v>
+        <v>74</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -4609,7 +4730,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4621,13 +4742,13 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>247</v>
+        <v>95</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>74</v>
@@ -4635,14 +4756,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4652,25 +4773,25 @@
         <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4720,7 +4841,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4735,25 +4856,25 @@
         <v>94</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>74</v>
+        <v>241</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4772,16 +4893,16 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4831,7 +4952,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4846,21 +4967,21 @@
         <v>94</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>196</v>
+        <v>74</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>95</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4874,7 +4995,7 @@
         <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4883,16 +5004,20 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>260</v>
+        <v>125</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>74</v>
       </c>
@@ -4940,7 +5065,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4955,25 +5080,25 @@
         <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>196</v>
+        <v>74</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>264</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>74</v>
+        <v>253</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4983,24 +5108,26 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K31" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>74</v>
@@ -5049,7 +5176,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5064,25 +5191,25 @@
         <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>196</v>
+        <v>74</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5092,25 +5219,25 @@
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K32" t="s" s="2">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5160,7 +5287,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5175,21 +5302,21 @@
         <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>196</v>
+        <v>74</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5212,18 +5339,20 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>74</v>
       </c>
@@ -5247,13 +5376,13 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>74</v>
+        <v>270</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>74</v>
+        <v>271</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -5271,7 +5400,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5286,10 +5415,10 @@
         <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>196</v>
+        <v>74</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>74</v>
@@ -5297,10 +5426,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5311,27 +5440,29 @@
         <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I34" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="J34" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>74</v>
@@ -5356,13 +5487,13 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>74</v>
+        <v>277</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>74</v>
+        <v>278</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -5380,13 +5511,13 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>93</v>
@@ -5395,10 +5526,10 @@
         <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>102</v>
+        <v>279</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>74</v>
+        <v>280</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>74</v>
@@ -5420,10 +5551,10 @@
         <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -5432,15 +5563,17 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>178</v>
+        <v>282</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>179</v>
+        <v>283</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -5465,13 +5598,13 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>74</v>
+        <v>286</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>74</v>
+        <v>287</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -5489,25 +5622,25 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>102</v>
+        <v>288</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>74</v>
+        <v>280</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>74</v>
@@ -5515,24 +5648,24 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5541,16 +5674,16 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>130</v>
+        <v>291</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>183</v>
+        <v>292</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>132</v>
+        <v>293</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5588,84 +5721,82 @@
         <v>74</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>184</v>
+        <v>289</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>95</v>
+        <v>294</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>74</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>187</v>
+        <v>297</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>188</v>
+        <v>298</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
       </c>
@@ -5713,50 +5844,50 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>189</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>74</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>285</v>
+        <v>74</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5765,17 +5896,15 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>178</v>
+        <v>301</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>74</v>
@@ -5824,10 +5953,10 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>81</v>
@@ -5839,21 +5968,21 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>74</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5861,13 +5990,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5876,17 +6005,15 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>104</v>
+        <v>301</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -5911,13 +6038,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>291</v>
+        <v>74</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>292</v>
+        <v>74</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5935,10 +6062,10 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>81</v>
@@ -5950,21 +6077,21 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>74</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5987,16 +6114,16 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6046,7 +6173,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6061,21 +6188,21 @@
         <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>74</v>
+        <v>295</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6089,7 +6216,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -6098,16 +6225,16 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6157,7 +6284,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6172,10 +6299,10 @@
         <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>277</v>
+        <v>318</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>74</v>
@@ -6183,10 +6310,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6197,10 +6324,10 @@
         <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -6209,17 +6336,15 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>74</v>
@@ -6244,13 +6369,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>304</v>
+        <v>74</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>305</v>
+        <v>74</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -6268,13 +6393,13 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>93</v>
@@ -6283,7 +6408,7 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>247</v>
+        <v>101</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>74</v>
@@ -6294,10 +6419,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6308,10 +6433,10 @@
         <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -6320,13 +6445,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>307</v>
+        <v>98</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>308</v>
+        <v>99</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6377,22 +6502,22 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>306</v>
+        <v>100</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>74</v>
@@ -6403,21 +6528,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>74</v>
@@ -6429,15 +6554,17 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>74</v>
@@ -6474,34 +6601,34 @@
         <v>74</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>74</v>
@@ -6512,14 +6639,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>128</v>
+        <v>228</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6532,24 +6659,26 @@
         <v>74</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>130</v>
+        <v>229</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -6585,19 +6714,19 @@
         <v>74</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6609,7 +6738,7 @@
         <v>93</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>95</v>
@@ -6623,46 +6752,44 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>186</v>
+        <v>326</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>187</v>
+        <v>327</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>188</v>
+        <v>328</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -6710,22 +6837,22 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>189</v>
+        <v>325</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>74</v>
@@ -6736,14 +6863,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>285</v>
+        <v>74</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6762,16 +6889,16 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6797,13 +6924,13 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>74</v>
+        <v>332</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>74</v>
+        <v>333</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -6821,7 +6948,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6836,10 +6963,10 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>247</v>
+        <v>334</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>74</v>
@@ -6847,10 +6974,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6864,7 +6991,7 @@
         <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>74</v>
@@ -6873,16 +7000,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6932,7 +7059,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -6947,10 +7074,10 @@
         <v>94</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>102</v>
+        <v>338</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>74</v>
@@ -6958,10 +7085,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6972,7 +7099,7 @@
         <v>75</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -6984,15 +7111,17 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>74</v>
@@ -7041,13 +7170,13 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>93</v>
@@ -7056,10 +7185,10 @@
         <v>94</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>102</v>
+        <v>318</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>74</v>
@@ -7067,10 +7196,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7093,15 +7222,17 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>178</v>
+        <v>282</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>179</v>
+        <v>343</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -7126,13 +7257,13 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>74</v>
+        <v>345</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>74</v>
+        <v>346</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -7150,7 +7281,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>181</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7159,13 +7290,13 @@
         <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>102</v>
+        <v>288</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>74</v>
@@ -7176,14 +7307,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7193,7 +7324,7 @@
         <v>76</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>74</v>
@@ -7202,17 +7333,15 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>130</v>
+        <v>348</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>74</v>
@@ -7249,19 +7378,19 @@
         <v>74</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>184</v>
+        <v>347</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7273,10 +7402,10 @@
         <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>74</v>
@@ -7287,46 +7416,42 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>187</v>
+        <v>98</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -7374,22 +7499,22 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>74</v>
@@ -7400,21 +7525,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>285</v>
+        <v>103</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -7426,16 +7551,16 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>325</v>
+        <v>105</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>326</v>
+        <v>106</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>243</v>
+        <v>107</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7473,34 +7598,34 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>324</v>
+        <v>111</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>247</v>
+        <v>95</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>74</v>
@@ -7511,42 +7636,46 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>328</v>
+        <v>229</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>74</v>
       </c>
@@ -7594,25 +7723,25 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>327</v>
+        <v>231</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>330</v>
+        <v>95</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>196</v>
+        <v>74</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>74</v>
@@ -7620,14 +7749,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>74</v>
+        <v>326</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7646,16 +7775,16 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>178</v>
+        <v>282</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>194</v>
+        <v>285</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7705,7 +7834,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7720,7 +7849,7 @@
         <v>94</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>102</v>
+        <v>288</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>74</v>
@@ -7731,10 +7860,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7745,10 +7874,10 @@
         <v>75</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>74</v>
@@ -7757,15 +7886,17 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>74</v>
@@ -7814,13 +7945,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>93</v>
@@ -7829,10 +7960,10 @@
         <v>94</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>74</v>
@@ -7840,10 +7971,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7854,10 +7985,10 @@
         <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>74</v>
@@ -7866,13 +7997,13 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>179</v>
+        <v>360</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>180</v>
+        <v>361</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7923,22 +8054,22 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>181</v>
+        <v>359</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>74</v>
@@ -7949,21 +8080,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -7975,17 +8106,15 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>74</v>
@@ -8022,34 +8151,34 @@
         <v>74</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>74</v>
@@ -8060,14 +8189,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8080,26 +8209,24 @@
         <v>74</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>187</v>
+        <v>105</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>74</v>
       </c>
@@ -8135,19 +8262,19 @@
         <v>74</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>189</v>
+        <v>111</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8159,7 +8286,7 @@
         <v>93</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>95</v>
@@ -8173,44 +8300,46 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>341</v>
+        <v>229</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>342</v>
+        <v>230</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>74</v>
       </c>
@@ -8258,22 +8387,22 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>340</v>
+        <v>231</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>247</v>
+        <v>95</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>74</v>
@@ -8284,21 +8413,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>74</v>
+        <v>326</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>74</v>
@@ -8310,16 +8439,16 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>344</v>
+        <v>282</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>347</v>
+        <v>285</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8369,22 +8498,22 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>348</v>
+        <v>94</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>349</v>
+        <v>288</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>74</v>
@@ -8395,10 +8524,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8409,7 +8538,7 @@
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -8421,17 +8550,15 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>74</v>
@@ -8480,13 +8607,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>93</v>
@@ -8495,10 +8622,10 @@
         <v>94</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>247</v>
+        <v>371</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>74</v>
@@ -8506,10 +8633,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8517,13 +8644,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>74</v>
@@ -8532,20 +8659,18 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>354</v>
+        <v>97</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>74</v>
       </c>
@@ -8593,10 +8718,10 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>81</v>
@@ -8605,13 +8730,13 @@
         <v>93</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>169</v>
+        <v>94</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>358</v>
+        <v>101</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>359</v>
+        <v>74</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>74</v>
@@ -8619,10 +8744,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8633,10 +8758,10 @@
         <v>75</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -8645,17 +8770,15 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>361</v>
+        <v>220</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>74</v>
@@ -8704,25 +8827,25 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>169</v>
+        <v>94</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>365</v>
+        <v>101</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>366</v>
+        <v>74</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>74</v>
@@ -8730,10 +8853,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8744,10 +8867,10 @@
         <v>75</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
@@ -8756,17 +8879,15 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>368</v>
+        <v>97</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>369</v>
+        <v>98</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>74</v>
@@ -8815,25 +8936,25 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>367</v>
+        <v>100</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>372</v>
+        <v>74</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>373</v>
+        <v>101</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>366</v>
+        <v>74</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>74</v>
@@ -8841,24 +8962,24 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>74</v>
@@ -8867,20 +8988,18 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>375</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>376</v>
+        <v>105</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>377</v>
+        <v>106</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>74</v>
       </c>
@@ -8916,37 +9035,37 @@
         <v>74</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>374</v>
+        <v>111</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>379</v>
+        <v>95</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>380</v>
+        <v>74</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>74</v>
@@ -8954,44 +9073,46 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I67" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I67" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="J67" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>382</v>
+        <v>229</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>383</v>
+        <v>230</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>74</v>
       </c>
@@ -9039,25 +9160,25 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>381</v>
+        <v>231</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>385</v>
+        <v>95</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>380</v>
+        <v>74</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>74</v>
@@ -9065,10 +9186,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9076,13 +9197,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>74</v>
@@ -9091,16 +9212,16 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>387</v>
+        <v>282</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>390</v>
+        <v>285</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9150,13 +9271,13 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>93</v>
@@ -9165,7 +9286,7 @@
         <v>94</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>391</v>
+        <v>288</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>74</v>
@@ -9176,10 +9297,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9193,25 +9314,25 @@
         <v>76</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>240</v>
+        <v>385</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>243</v>
+        <v>388</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9261,7 +9382,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9273,10 +9394,10 @@
         <v>93</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>94</v>
+        <v>389</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>230</v>
+        <v>390</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>74</v>
@@ -9287,10 +9408,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9301,10 +9422,10 @@
         <v>75</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>74</v>
@@ -9313,16 +9434,16 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>396</v>
+        <v>282</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>168</v>
+        <v>285</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9372,32 +9493,924 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>169</v>
+        <v>94</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>170</v>
+        <v>288</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM70">
+  <autoFilter ref="A1:AM78">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9407,7 +10420,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:09:12+00:00</t>
+    <t>2023-04-28T15:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="442">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -661,13 +661,13 @@
 </t>
   </si>
   <si>
-    <t>Numéro autorisation ARGHOS</t>
+    <t>numeroAutorisationARHGOS</t>
   </si>
   <si>
     <t>Unique instance identifiers assigned to a device by manufacturers other organizations or owners.</t>
   </si>
   <si>
-    <t>The barcode string from a barcode present on a device label or package may identify the instance, include names given to the device in local usage, or may identify the type of device. If the identifier identifies the type of device, Device.type element should be used.</t>
+    <t>Identifiant fonctionnel de l'autorisation ARHGOS de l'EML</t>
   </si>
   <si>
     <t>.id</t>
@@ -891,7 +891,7 @@
     <t>Device.status</t>
   </si>
   <si>
-    <t>active | inactive | entered-in-error | unknown</t>
+    <t>actif</t>
   </si>
   <si>
     <t>Status of the Device availability.</t>
@@ -963,10 +963,13 @@
     <t>Device.manufacturer</t>
   </si>
   <si>
+    <t>marque</t>
+  </si>
+  <si>
+    <t>A name of the manufacturer.</t>
+  </si>
+  <si>
     <t>Marque de l'équipement matériel lourd</t>
-  </si>
-  <si>
-    <t>A name of the manufacturer.</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].scoper.name</t>
@@ -1018,13 +1021,13 @@
     <t>Device.serialNumber</t>
   </si>
   <si>
+    <t>numeroSerie</t>
+  </si>
+  <si>
+    <t>The serial number assigned by the organization when the device was manufactured.</t>
+  </si>
+  <si>
     <t>Numéro de série de l'équipement matériel lourd</t>
-  </si>
-  <si>
-    <t>The serial number assigned by the organization when the device was manufactured.</t>
-  </si>
-  <si>
-    <t>Alphanumeric Maximum 20.</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].id</t>
@@ -1101,10 +1104,13 @@
     <t>The part number of the device.</t>
   </si>
   <si>
+    <t>Alphanumeric Maximum 20.</t>
+  </si>
+  <si>
     <t>Device.type</t>
   </si>
   <si>
-    <t>The kind or type of device</t>
+    <t>equipementMaterielLourd</t>
   </si>
   <si>
     <t>The kind or type of device.</t>
@@ -1284,11 +1290,11 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
-    <t>Référence vers la structure FINESS ET</t>
+    <t>idStructure</t>
   </si>
   <si>
     <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
@@ -4107,7 +4113,7 @@
         <v>76</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>74</v>
@@ -4218,7 +4224,7 @@
         <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>74</v>
@@ -4329,7 +4335,7 @@
         <v>76</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -5443,7 +5449,7 @@
         <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -5554,7 +5560,7 @@
         <v>76</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -5665,7 +5671,7 @@
         <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5776,7 +5782,7 @@
         <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5794,7 +5800,7 @@
         <v>298</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>236</v>
+        <v>299</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5859,7 +5865,7 @@
         <v>94</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>238</v>
@@ -5870,10 +5876,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5887,7 +5893,7 @@
         <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5896,13 +5902,13 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5953,7 +5959,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -5968,21 +5974,21 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>238</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5996,7 +6002,7 @@
         <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -6005,13 +6011,13 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6062,7 +6068,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -6077,21 +6083,21 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>238</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6105,7 +6111,7 @@
         <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -6117,10 +6123,10 @@
         <v>97</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>236</v>
@@ -6173,7 +6179,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6199,10 +6205,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6216,7 +6222,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -6228,13 +6234,13 @@
         <v>97</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6284,7 +6290,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6299,7 +6305,7 @@
         <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>238</v>
@@ -6310,10 +6316,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6327,7 +6333,7 @@
         <v>76</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -6339,10 +6345,10 @@
         <v>220</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6393,7 +6399,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -6419,10 +6425,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6528,10 +6534,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6639,10 +6645,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6752,14 +6758,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6781,10 +6787,10 @@
         <v>97</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>236</v>
@@ -6837,7 +6843,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6863,10 +6869,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6892,10 +6898,10 @@
         <v>160</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>236</v>
@@ -6927,10 +6933,10 @@
         <v>269</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -6948,7 +6954,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6963,7 +6969,7 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>238</v>
@@ -6974,10 +6980,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6991,7 +6997,7 @@
         <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>74</v>
@@ -7003,10 +7009,10 @@
         <v>97</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>236</v>
@@ -7059,7 +7065,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -7074,7 +7080,7 @@
         <v>94</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>238</v>
@@ -7085,10 +7091,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7102,7 +7108,7 @@
         <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>74</v>
@@ -7114,13 +7120,13 @@
         <v>97</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7170,7 +7176,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -7185,7 +7191,7 @@
         <v>94</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>238</v>
@@ -7196,10 +7202,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7213,7 +7219,7 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>74</v>
@@ -7225,10 +7231,10 @@
         <v>282</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>285</v>
@@ -7260,10 +7266,10 @@
         <v>269</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -7281,7 +7287,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7307,10 +7313,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7324,7 +7330,7 @@
         <v>76</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>74</v>
@@ -7336,10 +7342,10 @@
         <v>220</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7390,7 +7396,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7416,10 +7422,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7525,10 +7531,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7636,10 +7642,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7749,14 +7755,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7778,10 +7784,10 @@
         <v>282</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>285</v>
@@ -7834,7 +7840,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7860,10 +7866,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7889,10 +7895,10 @@
         <v>97</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>236</v>
@@ -7945,7 +7951,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7971,10 +7977,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7988,7 +7994,7 @@
         <v>76</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>74</v>
@@ -8000,10 +8006,10 @@
         <v>220</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8054,7 +8060,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8080,10 +8086,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8189,10 +8195,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8300,10 +8306,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8413,14 +8419,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8442,10 +8448,10 @@
         <v>282</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>285</v>
@@ -8498,7 +8504,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8524,10 +8530,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8553,10 +8559,10 @@
         <v>205</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8607,7 +8613,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -8622,7 +8628,7 @@
         <v>94</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>238</v>
@@ -8633,10 +8639,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8662,10 +8668,10 @@
         <v>97</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>236</v>
@@ -8718,7 +8724,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -8744,10 +8750,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8761,7 +8767,7 @@
         <v>76</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -8773,10 +8779,10 @@
         <v>220</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8827,7 +8833,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -8853,10 +8859,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8962,10 +8968,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9073,10 +9079,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9186,10 +9192,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9215,10 +9221,10 @@
         <v>282</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>285</v>
@@ -9271,7 +9277,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -9297,10 +9303,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9323,16 +9329,16 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9382,7 +9388,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9394,10 +9400,10 @@
         <v>93</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>74</v>
@@ -9408,10 +9414,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9437,10 +9443,10 @@
         <v>282</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>285</v>
@@ -9493,7 +9499,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9519,10 +9525,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9536,7 +9542,7 @@
         <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>74</v>
@@ -9545,19 +9551,19 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>216</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>74</v>
@@ -9606,7 +9612,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -9621,10 +9627,10 @@
         <v>217</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>74</v>
@@ -9632,10 +9638,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9658,16 +9664,16 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9717,7 +9723,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -9732,10 +9738,10 @@
         <v>217</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>74</v>
@@ -9743,10 +9749,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9760,7 +9766,7 @@
         <v>76</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>74</v>
@@ -9769,16 +9775,16 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9828,7 +9834,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -9840,13 +9846,13 @@
         <v>93</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>74</v>
@@ -9854,10 +9860,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9871,7 +9877,7 @@
         <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>74</v>
@@ -9880,19 +9886,19 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>216</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>74</v>
@@ -9941,7 +9947,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -9956,10 +9962,10 @@
         <v>217</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>74</v>
@@ -9967,10 +9973,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9984,7 +9990,7 @@
         <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>74</v>
@@ -9996,13 +10002,13 @@
         <v>125</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10052,7 +10058,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -10067,10 +10073,10 @@
         <v>94</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>74</v>
@@ -10078,10 +10084,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10095,7 +10101,7 @@
         <v>76</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>74</v>
@@ -10104,16 +10110,16 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10163,7 +10169,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -10178,7 +10184,7 @@
         <v>94</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>74</v>
@@ -10189,10 +10195,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10206,7 +10212,7 @@
         <v>76</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>74</v>
@@ -10218,10 +10224,10 @@
         <v>282</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>285</v>
@@ -10274,7 +10280,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -10300,10 +10306,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10317,7 +10323,7 @@
         <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>74</v>
@@ -10326,13 +10332,13 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>216</v>
@@ -10385,7 +10391,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9655,7 +9655,7 @@
         <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>74</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:34:44+00:00</t>
+    <t>2023-05-02T07:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="401">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T07:22:02+00:00</t>
+    <t>2023-05-02T14:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,7 +311,268 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Device.meta.id</t>
+    <t>Device.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Device.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Device.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Device.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>Device.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Device.extension:numberAuthorizationARHGOS</t>
+  </si>
+  <si>
+    <t>numberAuthorizationARHGOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/Device-numberAuthorizationARHGOS}
+</t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t>Device.extension:authorizationDateDevice</t>
+  </si>
+  <si>
+    <t>authorizationDateDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/Device-authorizationDateDevice}
+</t>
+  </si>
+  <si>
+    <t>Device.extension:periodImplantation</t>
+  </si>
+  <si>
+    <t>periodImplantation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-Period-implantation}
+</t>
+  </si>
+  <si>
+    <t>Dates de mise en oeuvre de l'EML</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte des dates de mise en oeuvre d’un équipement matériel lourd.</t>
+  </si>
+  <si>
+    <t>Device.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Device.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>numeroAutorisationARHGOS</t>
+  </si>
+  <si>
+    <t>Unique instance identifiers assigned to a device by manufacturers other organizations or owners.</t>
+  </si>
+  <si>
+    <t>Identifiant fonctionnel de l'autorisation ARHGOS de l'EML</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>The serial number which is a component of the production identifier (PI), a conditional, variable portion of a UDI.   The identifier.type code should be set to “SNO”(Serial Number) and the system left empty.</t>
+  </si>
+  <si>
+    <t>Device.definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DeviceDefinition)
+</t>
+  </si>
+  <si>
+    <t>The reference to the definition for the device</t>
+  </si>
+  <si>
+    <t>The reference to the definition for the device.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Unique Device Identifier (UDI) Barcode string</t>
+  </si>
+  <si>
+    <t>Unique device identifier (UDI) assigned to device label or package.  Note that the Device may include multiple udiCarriers as it either may include just the udiCarrier for the jurisdiction it is sold, or for multiple jurisdictions it could have been sold.</t>
+  </si>
+  <si>
+    <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
+  </si>
+  <si>
+    <t>.id and .code</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -327,404 +588,13 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Device.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
+    <t>Device.udiCarrier.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Device.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Device.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Device.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Device.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Device.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>Device.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Device.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Device.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Device.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Device.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>Device.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Device.extension:numberAuthorizationARHGOS</t>
-  </si>
-  <si>
-    <t>numberAuthorizationARHGOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/Device-numberAuthorizationARHGOS}
-</t>
-  </si>
-  <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>Device.extension:authorizationDateDevice</t>
-  </si>
-  <si>
-    <t>authorizationDateDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/Device-authorizationDateDevice}
-</t>
-  </si>
-  <si>
-    <t>Device.extension:periodImplantation</t>
-  </si>
-  <si>
-    <t>periodImplantation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-Period-implantation}
-</t>
-  </si>
-  <si>
-    <t>Dates de mise en oeuvre de l'EML</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte des dates de mise en oeuvre d’un équipement matériel lourd.</t>
-  </si>
-  <si>
-    <t>Device.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Device.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>numeroAutorisationARHGOS</t>
-  </si>
-  <si>
-    <t>Unique instance identifiers assigned to a device by manufacturers other organizations or owners.</t>
-  </si>
-  <si>
-    <t>Identifiant fonctionnel de l'autorisation ARHGOS de l'EML</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>The serial number which is a component of the production identifier (PI), a conditional, variable portion of a UDI.   The identifier.type code should be set to “SNO”(Serial Number) and the system left empty.</t>
-  </si>
-  <si>
-    <t>Device.definition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DeviceDefinition)
-</t>
-  </si>
-  <si>
-    <t>The reference to the definition for the device</t>
-  </si>
-  <si>
-    <t>The reference to the definition for the device.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
-    <t>Device.udiCarrier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Unique Device Identifier (UDI) Barcode string</t>
-  </si>
-  <si>
-    <t>Unique device identifier (UDI) assigned to device label or package.  Note that the Device may include multiple udiCarriers as it either may include just the udiCarrier for the jurisdiction it is sold, or for multiple jurisdictions it could have been sold.</t>
-  </si>
-  <si>
-    <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
-  </si>
-  <si>
-    <t>.id and .code</t>
-  </si>
-  <si>
-    <t>Device.udiCarrier.id</t>
-  </si>
-  <si>
-    <t>Device.udiCarrier.extension</t>
   </si>
   <si>
     <t>Device.udiCarrier.modifierExtension</t>
@@ -929,6 +799,9 @@
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>The availability status reason of the device.</t>
   </si>
   <si>
@@ -1290,7 +1163,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
@@ -1716,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM78"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.8515625" customWidth="true" bestFit="true"/>
@@ -1729,7 +1602,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="119.6484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="159.0546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1743,7 +1616,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="68.64453125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="112.0078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -2229,10 +2102,10 @@
         <v>74</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>97</v>
@@ -2243,7 +2116,9 @@
       <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>74</v>
@@ -2292,7 +2167,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -2301,13 +2176,13 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>74</v>
@@ -2318,21 +2193,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -2379,28 +2254,28 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>111</v>
@@ -2409,16 +2284,16 @@
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>74</v>
@@ -2429,14 +2304,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2452,19 +2327,19 @@
         <v>74</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2514,7 +2389,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -2529,7 +2404,7 @@
         <v>94</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>74</v>
@@ -2540,21 +2415,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -2563,19 +2438,19 @@
         <v>74</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2625,22 +2500,22 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>74</v>
@@ -2651,21 +2526,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>74</v>
@@ -2674,19 +2549,19 @@
         <v>74</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2724,34 +2599,34 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>74</v>
@@ -2762,12 +2637,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
@@ -2776,29 +2653,27 @@
         <v>75</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -2847,7 +2722,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -2859,10 +2734,10 @@
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>74</v>
@@ -2873,12 +2748,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2887,29 +2764,27 @@
         <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>74</v>
@@ -2934,13 +2809,13 @@
         <v>74</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>74</v>
@@ -2958,7 +2833,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2970,10 +2845,10 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>74</v>
@@ -2987,9 +2862,11 @@
         <v>146</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>74</v>
       </c>
@@ -2998,29 +2875,27 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>74</v>
@@ -3045,13 +2920,13 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -3069,7 +2944,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -3081,10 +2956,10 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>74</v>
@@ -3095,21 +2970,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -3118,21 +2993,23 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>74</v>
       </c>
@@ -3168,34 +3045,34 @@
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>74</v>
@@ -3206,10 +3083,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3220,10 +3097,10 @@
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>74</v>
@@ -3232,16 +3109,16 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3267,13 +3144,13 @@
         <v>74</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -3291,13 +3168,13 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>93</v>
@@ -3306,25 +3183,25 @@
         <v>94</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>74</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3343,16 +3220,16 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3402,7 +3279,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3414,10 +3291,10 @@
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>74</v>
@@ -3428,14 +3305,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3451,19 +3328,19 @@
         <v>74</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3513,7 +3390,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3522,16 +3399,16 @@
         <v>76</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>74</v>
@@ -3539,21 +3416,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -3565,17 +3442,15 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>74</v>
@@ -3612,34 +3487,34 @@
         <v>74</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>74</v>
@@ -3650,26 +3525,24 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>74</v>
@@ -3678,15 +3551,17 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>129</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>74</v>
@@ -3723,19 +3598,19 @@
         <v>74</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3747,7 +3622,7 @@
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>95</v>
@@ -3761,44 +3636,46 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I19" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="J19" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>129</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>74</v>
       </c>
@@ -3846,7 +3723,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3858,7 +3735,7 @@
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>95</v>
@@ -3872,16 +3749,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3891,24 +3766,26 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>74</v>
@@ -3957,59 +3834,59 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>74</v>
+        <v>195</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>74</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>200</v>
@@ -4018,11 +3895,9 @@
         <v>201</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O21" t="s" s="2">
         <v>202</v>
       </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>74</v>
       </c>
@@ -4058,48 +3933,48 @@
         <v>74</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>74</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4110,10 +3985,10 @@
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>74</v>
@@ -4122,7 +3997,7 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>205</v>
+        <v>97</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>206</v>
@@ -4131,9 +4006,11 @@
         <v>207</v>
       </c>
       <c r="N22" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>74</v>
       </c>
@@ -4181,13 +4058,13 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>93</v>
@@ -4199,22 +4076,22 @@
         <v>209</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>210</v>
+        <v>74</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>211</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>74</v>
+        <v>211</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4230,19 +4107,19 @@
         <v>74</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4292,7 +4169,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4304,35 +4181,35 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>217</v>
+        <v>94</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>74</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -4344,16 +4221,16 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4403,13 +4280,13 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>93</v>
@@ -4418,21 +4295,21 @@
         <v>94</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>210</v>
+        <v>74</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>74</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4455,16 +4332,20 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>98</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>74</v>
       </c>
@@ -4488,13 +4369,13 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>74</v>
+        <v>229</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -4512,7 +4393,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>100</v>
+        <v>223</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4521,13 +4402,13 @@
         <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>74</v>
@@ -4538,42 +4419,42 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4599,49 +4480,49 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>74</v>
+        <v>236</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>95</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>74</v>
@@ -4649,14 +4530,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4669,26 +4550,24 @@
         <v>74</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>74</v>
       </c>
@@ -4712,13 +4591,13 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>74</v>
+        <v>245</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -4736,7 +4615,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4748,13 +4627,13 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>74</v>
@@ -4762,14 +4641,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4785,19 +4664,19 @@
         <v>74</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4847,7 +4726,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4862,25 +4741,25 @@
         <v>94</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>239</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>241</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4890,7 +4769,7 @@
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>74</v>
@@ -4899,16 +4778,16 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4958,7 +4837,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4973,21 +4852,21 @@
         <v>94</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>246</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5010,20 +4889,16 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>125</v>
+        <v>261</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>74</v>
       </c>
@@ -5071,7 +4946,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -5086,25 +4961,25 @@
         <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>74</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>253</v>
+        <v>74</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5120,20 +4995,18 @@
         <v>74</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>74</v>
@@ -5182,7 +5055,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5197,25 +5070,25 @@
         <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>260</v>
+        <v>74</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5231,19 +5104,19 @@
         <v>74</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5293,7 +5166,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5308,21 +5181,21 @@
         <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5336,7 +5209,7 @@
         <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -5345,20 +5218,18 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>74</v>
       </c>
@@ -5382,13 +5253,13 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>270</v>
+        <v>74</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>271</v>
+        <v>74</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -5406,7 +5277,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5421,10 +5292,10 @@
         <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>74</v>
@@ -5432,10 +5303,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5446,29 +5317,27 @@
         <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>74</v>
@@ -5493,13 +5362,13 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>277</v>
+        <v>74</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>278</v>
+        <v>74</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -5517,13 +5386,13 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>93</v>
@@ -5532,10 +5401,10 @@
         <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>102</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>280</v>
+        <v>74</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>74</v>
@@ -5543,10 +5412,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5557,7 +5426,7 @@
         <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>74</v>
@@ -5569,17 +5438,15 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -5604,13 +5471,13 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>286</v>
+        <v>74</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>287</v>
+        <v>74</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -5628,25 +5495,25 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>288</v>
+        <v>102</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>280</v>
+        <v>74</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>74</v>
@@ -5654,21 +5521,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>290</v>
+        <v>128</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
@@ -5680,16 +5547,16 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>291</v>
+        <v>130</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>292</v>
+        <v>183</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>293</v>
+        <v>132</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5727,82 +5594,84 @@
         <v>74</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>289</v>
+        <v>184</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>294</v>
+        <v>95</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>295</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I37" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="J37" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>297</v>
+        <v>187</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>298</v>
+        <v>188</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
       </c>
@@ -5850,44 +5719,44 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>296</v>
+        <v>189</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>300</v>
+        <v>95</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>74</v>
+        <v>286</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>81</v>
@@ -5902,15 +5771,17 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>302</v>
+        <v>178</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>74</v>
@@ -5959,10 +5830,10 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>81</v>
@@ -5974,21 +5845,21 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>305</v>
+        <v>102</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>306</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5996,7 +5867,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>81</v>
@@ -6011,15 +5882,17 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>302</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -6044,13 +5917,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>74</v>
+        <v>292</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>74</v>
+        <v>293</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -6068,10 +5941,10 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>81</v>
@@ -6083,21 +5956,21 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>311</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6120,16 +5993,16 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6179,7 +6052,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6194,21 +6067,21 @@
         <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>295</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6222,7 +6095,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -6231,16 +6104,16 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6290,7 +6163,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6305,10 +6178,10 @@
         <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>74</v>
@@ -6316,10 +6189,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6330,10 +6203,10 @@
         <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -6342,15 +6215,17 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>74</v>
@@ -6375,13 +6250,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>74</v>
+        <v>306</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>74</v>
+        <v>307</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -6399,13 +6274,13 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>93</v>
@@ -6414,7 +6289,7 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>101</v>
+        <v>247</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>74</v>
@@ -6425,10 +6300,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6439,7 +6314,7 @@
         <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>74</v>
@@ -6451,13 +6326,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>98</v>
+        <v>309</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>99</v>
+        <v>310</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6508,22 +6383,22 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>100</v>
+        <v>308</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>74</v>
@@ -6534,21 +6409,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>74</v>
@@ -6560,17 +6435,15 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>74</v>
@@ -6607,34 +6480,34 @@
         <v>74</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>74</v>
@@ -6645,14 +6518,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>228</v>
+        <v>128</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6665,26 +6538,24 @@
         <v>74</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>229</v>
+        <v>130</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -6720,19 +6591,19 @@
         <v>74</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6744,7 +6615,7 @@
         <v>93</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>95</v>
@@ -6758,44 +6629,46 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>327</v>
+        <v>186</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>328</v>
+        <v>187</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>329</v>
+        <v>188</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -6843,22 +6716,22 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>326</v>
+        <v>189</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>74</v>
@@ -6869,14 +6742,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>74</v>
+        <v>286</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6895,16 +6768,16 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6930,13 +6803,13 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>333</v>
+        <v>74</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>334</v>
+        <v>74</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -6954,7 +6827,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6969,10 +6842,10 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>335</v>
+        <v>247</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>74</v>
@@ -6980,10 +6853,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7006,16 +6879,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7065,7 +6938,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -7080,10 +6953,10 @@
         <v>94</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>339</v>
+        <v>102</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>74</v>
@@ -7091,10 +6964,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7105,7 +6978,7 @@
         <v>75</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -7117,17 +6990,15 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>74</v>
@@ -7176,13 +7047,13 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>93</v>
@@ -7191,10 +7062,10 @@
         <v>94</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>319</v>
+        <v>102</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>74</v>
@@ -7202,10 +7073,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7219,7 +7090,7 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>74</v>
@@ -7228,17 +7099,15 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>345</v>
+        <v>179</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -7263,13 +7132,13 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>347</v>
+        <v>74</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>348</v>
+        <v>74</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -7287,7 +7156,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>344</v>
+        <v>181</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7296,13 +7165,13 @@
         <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>288</v>
+        <v>102</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>74</v>
@@ -7313,14 +7182,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7339,15 +7208,17 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>350</v>
+        <v>130</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>74</v>
@@ -7384,19 +7255,19 @@
         <v>74</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>349</v>
+        <v>184</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7408,10 +7279,10 @@
         <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>74</v>
@@ -7422,42 +7293,46 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>98</v>
+        <v>187</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -7505,22 +7380,22 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>74</v>
@@ -7531,21 +7406,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -7557,16 +7432,16 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>105</v>
+        <v>327</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>106</v>
+        <v>328</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7604,34 +7479,34 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>111</v>
+        <v>326</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>74</v>
@@ -7642,46 +7517,42 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>354</v>
+        <v>329</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>354</v>
+        <v>329</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>229</v>
+        <v>330</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>74</v>
       </c>
@@ -7729,25 +7600,25 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>231</v>
+        <v>329</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>95</v>
+        <v>332</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>74</v>
@@ -7755,14 +7626,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>327</v>
+        <v>74</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7781,16 +7652,16 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>285</v>
+        <v>194</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7840,7 +7711,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7855,7 +7726,7 @@
         <v>94</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>288</v>
+        <v>102</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>74</v>
@@ -7866,10 +7737,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7880,7 +7751,7 @@
         <v>75</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>74</v>
@@ -7892,17 +7763,15 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>74</v>
@@ -7951,13 +7820,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>93</v>
@@ -7966,10 +7835,10 @@
         <v>94</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>74</v>
@@ -7977,10 +7846,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7991,7 +7860,7 @@
         <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>74</v>
@@ -8003,13 +7872,13 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>362</v>
+        <v>179</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>363</v>
+        <v>180</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8060,22 +7929,22 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>361</v>
+        <v>181</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>74</v>
@@ -8086,21 +7955,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -8112,15 +7981,17 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>74</v>
@@ -8157,34 +8028,34 @@
         <v>74</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>74</v>
@@ -8195,14 +8066,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8215,24 +8086,26 @@
         <v>74</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>74</v>
       </c>
@@ -8268,19 +8141,19 @@
         <v>74</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8292,7 +8165,7 @@
         <v>93</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>95</v>
@@ -8306,46 +8179,44 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>229</v>
+        <v>343</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>230</v>
+        <v>344</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>74</v>
       </c>
@@ -8393,22 +8264,22 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>231</v>
+        <v>342</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>74</v>
@@ -8419,21 +8290,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>327</v>
+        <v>74</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>74</v>
@@ -8445,16 +8316,16 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>282</v>
+        <v>346</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>285</v>
+        <v>349</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8504,22 +8375,22 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>94</v>
+        <v>350</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>288</v>
+        <v>351</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>74</v>
@@ -8530,10 +8401,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8544,7 +8415,7 @@
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -8556,15 +8427,17 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>74</v>
@@ -8613,13 +8486,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>93</v>
@@ -8628,10 +8501,10 @@
         <v>94</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>373</v>
+        <v>247</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>74</v>
@@ -8639,10 +8512,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8650,7 +8523,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>81</v>
@@ -8665,18 +8538,20 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>97</v>
+        <v>356</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>74</v>
       </c>
@@ -8724,10 +8599,10 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>81</v>
@@ -8736,13 +8611,13 @@
         <v>93</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>101</v>
+        <v>360</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>74</v>
+        <v>361</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>74</v>
@@ -8750,10 +8625,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8764,10 +8639,10 @@
         <v>75</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -8776,15 +8651,17 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>220</v>
+        <v>363</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>74</v>
@@ -8833,25 +8710,25 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>101</v>
+        <v>367</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>74</v>
+        <v>368</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>74</v>
@@ -8859,10 +8736,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8873,7 +8750,7 @@
         <v>75</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>74</v>
@@ -8885,15 +8762,17 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>97</v>
+        <v>370</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>98</v>
+        <v>371</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>74</v>
@@ -8942,25 +8821,25 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>100</v>
+        <v>369</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>74</v>
+        <v>374</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>101</v>
+        <v>375</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>74</v>
+        <v>368</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>74</v>
@@ -8968,21 +8847,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -8994,18 +8873,20 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>377</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>105</v>
+        <v>378</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>106</v>
+        <v>379</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>74</v>
       </c>
@@ -9041,37 +8922,37 @@
         <v>74</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>111</v>
+        <v>376</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>95</v>
+        <v>381</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>74</v>
+        <v>382</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>74</v>
@@ -9079,46 +8960,44 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>229</v>
+        <v>384</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>230</v>
+        <v>385</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>74</v>
       </c>
@@ -9166,25 +9045,25 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>231</v>
+        <v>383</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>95</v>
+        <v>387</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>74</v>
+        <v>382</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>74</v>
@@ -9192,10 +9071,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9203,10 +9082,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>74</v>
@@ -9218,16 +9097,16 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>282</v>
+        <v>389</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>285</v>
+        <v>392</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9277,13 +9156,13 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>93</v>
@@ -9292,7 +9171,7 @@
         <v>94</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>288</v>
+        <v>393</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>74</v>
@@ -9303,10 +9182,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9326,19 +9205,19 @@
         <v>74</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>387</v>
+        <v>240</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>390</v>
+        <v>243</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9388,7 +9267,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9400,10 +9279,10 @@
         <v>93</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>391</v>
+        <v>94</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>392</v>
+        <v>230</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>74</v>
@@ -9414,10 +9293,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9428,7 +9307,7 @@
         <v>75</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>74</v>
@@ -9440,16 +9319,16 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>282</v>
+        <v>398</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>285</v>
+        <v>168</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9499,924 +9378,32 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>288</v>
+        <v>170</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM78" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM78">
+  <autoFilter ref="A1:AM70">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10426,7 +9413,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:32:14+00:00</t>
+    <t>2023-05-02T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:46:32+00:00</t>
+    <t>2023-05-04T14:01:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-device.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="403">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:08:50+00:00</t>
+    <t>2023-05-05T17:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -447,36 +447,45 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Device.extension:numberAuthorizationARHGOS</t>
-  </si>
-  <si>
-    <t>numberAuthorizationARHGOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/Device-numberAuthorizationARHGOS}
+    <t>Device.extension:as-ext-device-number-authorization-arhgos</t>
+  </si>
+  <si>
+    <t>as-ext-device-number-authorization-arhgos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-number-authorization-arhgos}
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>Device.extension:authorizationDateDevice</t>
-  </si>
-  <si>
-    <t>authorizationDateDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/Device-authorizationDateDevice}
+    <t>numeroAutorisationARHGOS</t>
+  </si>
+  <si>
+    <t>Identifiant fonctionnel de l'autorisation ARHGOS de l'EML.</t>
+  </si>
+  <si>
+    <t>Device.extension:as-ext-device-authorization-date-device</t>
+  </si>
+  <si>
+    <t>as-ext-device-authorization-date-device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-authorization-date-device}
 </t>
   </si>
   <si>
-    <t>Device.extension:periodImplantation</t>
-  </si>
-  <si>
-    <t>periodImplantation</t>
+    <t>dateDecision</t>
+  </si>
+  <si>
+    <t>Date de délivrance de l’autorisation d’EML.</t>
+  </si>
+  <si>
+    <t>Synonyme FINESS : date d’autorisation.</t>
+  </si>
+  <si>
+    <t>Device.extension:as-ext-device-Period-implantation</t>
+  </si>
+  <si>
+    <t>as-ext-device-Period-implantation</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-device-Period-implantation}
@@ -510,9 +519,6 @@
   <si>
     <t xml:space="preserve">Identifier
 </t>
-  </si>
-  <si>
-    <t>numeroAutorisationARHGOS</t>
   </si>
   <si>
     <t>Unique instance identifiers assigned to a device by manufacturers other organizations or owners.</t>
@@ -1173,7 +1179,7 @@
     <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
   </si>
   <si>
-    <t>Reference vers l'id de la ressource de la structure FINESS ET à laquelle est rattaché cet équipement matériel lourd</t>
+    <t>Référence vers l'id de la ressource de la structure FINESS ET à laquelle est rattaché cet équipement matériel lourd.</t>
   </si>
   <si>
     <t>.playedRole[typeCode=OWN].scoper</t>
@@ -1592,9 +1598,9 @@
   <dimension ref="A1:AM70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.8515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.40625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.6015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.4140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="40.96875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2737,7 +2743,7 @@
         <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>74</v>
@@ -2779,12 +2785,14 @@
         <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>74</v>
@@ -2848,7 +2856,7 @@
         <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>74</v>
@@ -2859,13 +2867,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>74</v>
@@ -2887,13 +2895,13 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2970,10 +2978,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2999,16 +3007,16 @@
         <v>129</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>74</v>
@@ -3057,7 +3065,7 @@
         <v>135</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -3083,10 +3091,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3109,16 +3117,16 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3168,7 +3176,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -3183,21 +3191,21 @@
         <v>94</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3220,16 +3228,16 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3279,7 +3287,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3291,10 +3299,10 @@
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>74</v>
@@ -3305,10 +3313,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3331,16 +3339,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3390,7 +3398,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3405,10 +3413,10 @@
         <v>94</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>74</v>
@@ -3416,10 +3424,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3442,13 +3450,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3499,7 +3507,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -3525,10 +3533,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3557,7 +3565,7 @@
         <v>130</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>132</v>
@@ -3610,7 +3618,7 @@
         <v>135</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3636,14 +3644,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3665,16 +3673,16 @@
         <v>129</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>74</v>
@@ -3723,7 +3731,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3749,14 +3757,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3775,16 +3783,16 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3834,7 +3842,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3849,25 +3857,25 @@
         <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3889,13 +3897,13 @@
         <v>97</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3945,7 +3953,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3960,21 +3968,21 @@
         <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4000,16 +4008,16 @@
         <v>97</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>74</v>
@@ -4058,7 +4066,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -4073,7 +4081,7 @@
         <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>74</v>
@@ -4084,14 +4092,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4110,16 +4118,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4169,7 +4177,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4184,25 +4192,25 @@
         <v>94</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4221,16 +4229,16 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4280,7 +4288,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -4295,21 +4303,21 @@
         <v>94</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4335,16 +4343,16 @@
         <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>74</v>
@@ -4369,13 +4377,13 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -4393,7 +4401,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4408,7 +4416,7 @@
         <v>94</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>74</v>
@@ -4419,10 +4427,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4448,13 +4456,13 @@
         <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4480,13 +4488,13 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -4504,7 +4512,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4519,10 +4527,10 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>74</v>
@@ -4530,10 +4538,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4556,16 +4564,16 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4591,13 +4599,13 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -4615,7 +4623,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4630,10 +4638,10 @@
         <v>94</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>74</v>
@@ -4641,14 +4649,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4667,16 +4675,16 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4726,7 +4734,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4741,21 +4749,21 @@
         <v>94</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4778,16 +4786,16 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4837,7 +4845,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4852,10 +4860,10 @@
         <v>94</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>95</v>
@@ -4863,10 +4871,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4889,13 +4897,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4946,7 +4954,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4961,21 +4969,21 @@
         <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4998,13 +5006,13 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5055,7 +5063,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5070,21 +5078,21 @@
         <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5107,16 +5115,16 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5166,7 +5174,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5181,21 +5189,21 @@
         <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5218,16 +5226,16 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5277,7 +5285,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5292,10 +5300,10 @@
         <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>74</v>
@@ -5303,10 +5311,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5329,13 +5337,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5386,7 +5394,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5412,10 +5420,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5438,13 +5446,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5495,7 +5503,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5521,10 +5529,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5553,7 +5561,7 @@
         <v>130</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>132</v>
@@ -5606,7 +5614,7 @@
         <v>135</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5632,14 +5640,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5661,16 +5669,16 @@
         <v>129</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -5719,7 +5727,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -5745,14 +5753,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5771,16 +5779,16 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5830,7 +5838,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5856,10 +5864,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5885,13 +5893,13 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5917,13 +5925,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5941,7 +5949,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5956,10 +5964,10 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>74</v>
@@ -5967,10 +5975,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5993,16 +6001,16 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6052,7 +6060,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6067,10 +6075,10 @@
         <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>74</v>
@@ -6078,10 +6086,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6104,16 +6112,16 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6163,7 +6171,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6178,10 +6186,10 @@
         <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>74</v>
@@ -6189,10 +6197,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6215,16 +6223,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6250,13 +6258,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -6274,7 +6282,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -6289,7 +6297,7 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>74</v>
@@ -6300,10 +6308,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6326,13 +6334,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6383,7 +6391,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -6409,10 +6417,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6435,13 +6443,13 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6492,7 +6500,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6518,10 +6526,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6550,7 +6558,7 @@
         <v>130</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>132</v>
@@ -6603,7 +6611,7 @@
         <v>135</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6629,14 +6637,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6658,16 +6666,16 @@
         <v>129</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
@@ -6716,7 +6724,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -6742,14 +6750,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6768,16 +6776,16 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6827,7 +6835,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6842,7 +6850,7 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>74</v>
@@ -6853,10 +6861,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6879,16 +6887,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6938,7 +6946,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -6956,7 +6964,7 @@
         <v>102</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>74</v>
@@ -6964,10 +6972,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6990,13 +6998,13 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7047,7 +7055,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -7073,10 +7081,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7099,13 +7107,13 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7156,7 +7164,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7182,10 +7190,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7214,7 +7222,7 @@
         <v>130</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>132</v>
@@ -7267,7 +7275,7 @@
         <v>135</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7293,14 +7301,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7322,16 +7330,16 @@
         <v>129</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
@@ -7380,7 +7388,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -7406,14 +7414,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7432,16 +7440,16 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7491,7 +7499,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7506,7 +7514,7 @@
         <v>94</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>74</v>
@@ -7517,10 +7525,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7543,13 +7551,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7600,7 +7608,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -7615,10 +7623,10 @@
         <v>94</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>74</v>
@@ -7626,10 +7634,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7652,16 +7660,16 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7711,7 +7719,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7737,10 +7745,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7763,13 +7771,13 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7820,7 +7828,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7846,10 +7854,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7872,13 +7880,13 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7929,7 +7937,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7955,10 +7963,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7987,7 +7995,7 @@
         <v>130</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>132</v>
@@ -8040,7 +8048,7 @@
         <v>135</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -8066,14 +8074,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8095,16 +8103,16 @@
         <v>129</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>74</v>
@@ -8153,7 +8161,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8179,10 +8187,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8205,16 +8213,16 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8264,7 +8272,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -8279,7 +8287,7 @@
         <v>94</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>74</v>
@@ -8290,10 +8298,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8316,16 +8324,16 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8375,7 +8383,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8387,10 +8395,10 @@
         <v>93</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>74</v>
@@ -8401,10 +8409,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8427,16 +8435,16 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8486,7 +8494,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -8501,7 +8509,7 @@
         <v>94</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>74</v>
@@ -8512,10 +8520,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8538,19 +8546,19 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>74</v>
@@ -8599,7 +8607,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -8611,13 +8619,13 @@
         <v>93</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>74</v>
@@ -8625,10 +8633,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8651,16 +8659,16 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8710,7 +8718,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -8722,13 +8730,13 @@
         <v>93</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>74</v>
@@ -8736,10 +8744,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8762,16 +8770,16 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8821,7 +8829,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -8833,13 +8841,13 @@
         <v>93</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>74</v>
@@ -8847,10 +8855,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8873,19 +8881,19 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>74</v>
@@ -8934,7 +8942,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -8946,13 +8954,13 @@
         <v>93</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>74</v>
@@ -8960,10 +8968,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8989,13 +8997,13 @@
         <v>97</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9045,7 +9053,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
@@ -9060,10 +9068,10 @@
         <v>94</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>74</v>
@@ -9071,10 +9079,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9097,16 +9105,16 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9156,7 +9164,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -9171,7 +9179,7 @@
         <v>94</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>74</v>
@@ -9182,10 +9190,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9208,16 +9216,16 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9267,7 +9275,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9282,7 +9290,7 @@
         <v>94</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>74</v>
@@ -9293,10 +9301,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9319,16 +9327,16 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9378,7 +9386,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9390,10 +9398,10 @@
         <v>93</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>74</v>
